--- a/uebung2/uebung2_daten.xlsx
+++ b/uebung2/uebung2_daten.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ms_sql_pr\trainingDB\uebung2\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D62669A6-9184-4921-8870-504421EED1A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -18,9 +24,260 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="82">
+  <si>
+    <t xml:space="preserve">MA_id </t>
+  </si>
+  <si>
+    <t xml:space="preserve">nname </t>
+  </si>
+  <si>
+    <t xml:space="preserve">vname </t>
+  </si>
+  <si>
+    <t xml:space="preserve">str_hsnr </t>
+  </si>
+  <si>
+    <t xml:space="preserve">plz </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ort </t>
+  </si>
+  <si>
+    <t xml:space="preserve">gebdatum </t>
+  </si>
+  <si>
+    <t xml:space="preserve">fambez </t>
+  </si>
+  <si>
+    <t xml:space="preserve">abtbez </t>
+  </si>
+  <si>
+    <t xml:space="preserve">azBez </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fahrer </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bob </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mozartstr. 7 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fuerth </t>
+  </si>
+  <si>
+    <t xml:space="preserve">eingetr. Lebensgemein-schaft </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Produktion </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vollzeit </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platz </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alexander </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lessingstr. 72 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Erlangen </t>
+  </si>
+  <si>
+    <t xml:space="preserve">verheiratet </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kreuz </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Andreas </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ringstr. 40 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">geschieden </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vertrieb </t>
+  </si>
+  <si>
+    <t xml:space="preserve">HomeOffice </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Geber </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ann </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Schillerstr. 25 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verwaltung </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zug </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lindenweg 12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuernberg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minijob </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bolika </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anna </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bahnhofstr. 142 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entwicklung </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nass </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dorfstr. 18 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Theke </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kirchplatz 60 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">verwitwet </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teilzeit </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Höhle </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Axel </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mühlgasse 94 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diener </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bernhard </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mühlgasse 69 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marketing </t>
+  </si>
+  <si>
+    <t>Tabelle Arbeitszeitmodell</t>
+  </si>
+  <si>
+    <t>Tabelle Familienstand</t>
+  </si>
+  <si>
+    <t>modell_code</t>
+  </si>
+  <si>
+    <t>azBez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">f_id </t>
+  </si>
+  <si>
+    <t>fambez</t>
+  </si>
+  <si>
+    <t>ho</t>
+  </si>
+  <si>
+    <t>HomeOffice</t>
+  </si>
+  <si>
+    <t>ledig</t>
+  </si>
+  <si>
+    <t>tz</t>
+  </si>
+  <si>
+    <t>Teilzeit</t>
+  </si>
+  <si>
+    <t>verheiratet</t>
+  </si>
+  <si>
+    <t>vz</t>
+  </si>
+  <si>
+    <t>Vollzeit</t>
+  </si>
+  <si>
+    <t>geschieden</t>
+  </si>
+  <si>
+    <t>mm</t>
+  </si>
+  <si>
+    <t>Minijob</t>
+  </si>
+  <si>
+    <t>verwitwet</t>
+  </si>
+  <si>
+    <t>eingetr. Lebensgemeinschaft</t>
+  </si>
+  <si>
+    <t>Tabelle Abteilung</t>
+  </si>
+  <si>
+    <t>antnr abtbez</t>
+  </si>
+  <si>
+    <t>Geschäftsführung</t>
+  </si>
+  <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>Sekretariat</t>
+  </si>
+  <si>
+    <t>Allgemeine Verwaltung</t>
+  </si>
+  <si>
+    <t>Einkauf</t>
+  </si>
+  <si>
+    <t>Verkauf</t>
+  </si>
+  <si>
+    <t>Buchhaltung</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -28,16 +285,52 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9D9D9"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -45,15 +338,94 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -330,10 +702,734 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K31"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="2.109375" customWidth="1"/>
+    <col min="2" max="2" width="10.109375" customWidth="1"/>
+    <col min="3" max="3" width="12.5546875" customWidth="1"/>
+    <col min="4" max="4" width="20.6640625" customWidth="1"/>
+    <col min="5" max="5" width="24.5546875" customWidth="1"/>
+    <col min="6" max="6" width="13.6640625" customWidth="1"/>
+    <col min="7" max="7" width="16.77734375" customWidth="1"/>
+    <col min="8" max="8" width="17.44140625" customWidth="1"/>
+    <col min="9" max="9" width="43.5546875" customWidth="1"/>
+    <col min="10" max="10" width="20.109375" customWidth="1"/>
+    <col min="11" max="11" width="18.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" s="1"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+    </row>
+    <row r="2" spans="1:11" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A2" s="1"/>
+      <c r="B2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A3" s="1"/>
+      <c r="B3" s="3">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="3">
+        <v>90768</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="4">
+        <v>26605</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A4" s="1"/>
+      <c r="B4" s="3">
+        <v>2</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="3">
+        <v>91054</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" s="4">
+        <v>20302</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A5" s="1"/>
+      <c r="B5" s="3">
+        <v>3</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" s="3">
+        <v>90765</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" s="4">
+        <v>27145</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A6" s="1"/>
+      <c r="B6" s="3">
+        <v>4</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6" s="3">
+        <v>90762</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" s="4">
+        <v>31853</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A7" s="1"/>
+      <c r="B7" s="3">
+        <v>5</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F7" s="3">
+        <v>90411</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H7" s="4">
+        <v>35144</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A8" s="1"/>
+      <c r="B8" s="3">
+        <v>6</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F8" s="3">
+        <v>90425</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H8" s="4">
+        <v>29696</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A9" s="1"/>
+      <c r="B9" s="3">
+        <v>7</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F9" s="3">
+        <v>90409</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H9" s="4">
+        <v>21591</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A10" s="1"/>
+      <c r="B10" s="3">
+        <v>8</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F10" s="3">
+        <v>91052</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H10" s="4">
+        <v>23399</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A11" s="1"/>
+      <c r="B11" s="3">
+        <v>9</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F11" s="3">
+        <v>90766</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H11" s="4">
+        <v>25419</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A12" s="1"/>
+      <c r="B12" s="3">
+        <v>10</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F12" s="3">
+        <v>90763</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H12" s="4">
+        <v>22429</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16" s="1"/>
+      <c r="B16" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C16" s="10"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="I16" s="11"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17" s="1"/>
+      <c r="B17" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A18" s="1"/>
+      <c r="B18" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="7">
+        <v>1</v>
+      </c>
+      <c r="I18" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19" s="1"/>
+      <c r="B19" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="7">
+        <v>2</v>
+      </c>
+      <c r="I19" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A20" s="1"/>
+      <c r="B20" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="7">
+        <v>3</v>
+      </c>
+      <c r="I20" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A21" s="1"/>
+      <c r="B21" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="7">
+        <v>4</v>
+      </c>
+      <c r="I21" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="J21" s="1"/>
+      <c r="K21" s="1"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A22" s="1"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="7">
+        <v>5</v>
+      </c>
+      <c r="I22" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="J22" s="1"/>
+      <c r="K22" s="1"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A23" s="1"/>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="E23" s="10"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1"/>
+      <c r="K23" s="1"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A24" s="1"/>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1"/>
+      <c r="K24" s="1"/>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A25" s="1"/>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="7">
+        <v>1</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+      <c r="J25" s="1"/>
+      <c r="K25" s="1"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A26" s="1"/>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="7">
+        <v>2</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1"/>
+      <c r="K26" s="1"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A27" s="1"/>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="7">
+        <v>3</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1"/>
+      <c r="K27" s="1"/>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A28" s="1"/>
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="7">
+        <v>4</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1"/>
+      <c r="K28" s="1"/>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A29" s="1"/>
+      <c r="B29" s="1"/>
+      <c r="C29" s="1"/>
+      <c r="D29" s="7">
+        <v>5</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1"/>
+      <c r="K29" s="1"/>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A30" s="1"/>
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="7">
+        <v>6</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1"/>
+      <c r="K30" s="1"/>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A31" s="1"/>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="7">
+        <v>7</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1"/>
+      <c r="K31" s="1"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="D23:E23"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/uebung2/uebung2_daten.xlsx
+++ b/uebung2/uebung2_daten.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ms_sql_pr\trainingDB\uebung2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D62669A6-9184-4921-8870-504421EED1A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8B250F3-F7A7-4161-9975-76727CEDA699}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -394,7 +394,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -405,6 +405,9 @@
     </xf>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -421,6 +424,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -711,7 +717,7 @@
     <col min="3" max="3" width="12.5546875" customWidth="1"/>
     <col min="4" max="4" width="20.6640625" customWidth="1"/>
     <col min="5" max="5" width="24.5546875" customWidth="1"/>
-    <col min="6" max="6" width="13.6640625" customWidth="1"/>
+    <col min="6" max="6" width="20.44140625" customWidth="1"/>
     <col min="7" max="7" width="16.77734375" customWidth="1"/>
     <col min="8" max="8" width="17.44140625" customWidth="1"/>
     <col min="9" max="9" width="43.5546875" customWidth="1"/>
@@ -1136,37 +1142,41 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="C16" s="10"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
+      <c r="C16" s="11"/>
+      <c r="E16" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F16" s="13"/>
       <c r="G16" s="1"/>
-      <c r="H16" s="9" t="s">
+      <c r="H16" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="I16" s="11"/>
+      <c r="I16" s="12"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
+      <c r="E17" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>74</v>
+      </c>
       <c r="G17" s="1"/>
-      <c r="H17" s="6" t="s">
+      <c r="H17" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="I17" s="5" t="s">
+      <c r="I17" s="6" t="s">
         <v>59</v>
       </c>
       <c r="J17" s="1"/>
@@ -1174,20 +1184,23 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="C18" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
+      <c r="E18" s="8">
+        <v>1</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>75</v>
+      </c>
       <c r="G18" s="1"/>
-      <c r="H18" s="7">
+      <c r="H18" s="8">
         <v>1</v>
       </c>
-      <c r="I18" s="8" t="s">
+      <c r="I18" s="9" t="s">
         <v>62</v>
       </c>
       <c r="J18" s="1"/>
@@ -1195,20 +1208,23 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
-      <c r="B19" s="7" t="s">
+      <c r="B19" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="C19" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
+      <c r="E19" s="8">
+        <v>2</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>76</v>
+      </c>
       <c r="G19" s="1"/>
-      <c r="H19" s="7">
+      <c r="H19" s="8">
         <v>2</v>
       </c>
-      <c r="I19" s="8" t="s">
+      <c r="I19" s="9" t="s">
         <v>65</v>
       </c>
       <c r="J19" s="1"/>
@@ -1216,20 +1232,23 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
-      <c r="B20" s="7" t="s">
+      <c r="B20" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="C20" s="8" t="s">
+      <c r="C20" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
+      <c r="E20" s="8">
+        <v>3</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>77</v>
+      </c>
       <c r="G20" s="1"/>
-      <c r="H20" s="7">
+      <c r="H20" s="8">
         <v>3</v>
       </c>
-      <c r="I20" s="8" t="s">
+      <c r="I20" s="9" t="s">
         <v>68</v>
       </c>
       <c r="J20" s="1"/>
@@ -1237,20 +1256,23 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
-      <c r="B21" s="7" t="s">
+      <c r="B21" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="C21" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
+      <c r="E21" s="8">
+        <v>4</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>78</v>
+      </c>
       <c r="G21" s="1"/>
-      <c r="H21" s="7">
+      <c r="H21" s="8">
         <v>4</v>
       </c>
-      <c r="I21" s="8" t="s">
+      <c r="I21" s="9" t="s">
         <v>71</v>
       </c>
       <c r="J21" s="1"/>
@@ -1260,14 +1282,17 @@
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
+      <c r="E22" s="8">
+        <v>5</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>79</v>
+      </c>
       <c r="G22" s="1"/>
-      <c r="H22" s="7">
+      <c r="H22" s="8">
         <v>5</v>
       </c>
-      <c r="I22" s="8" t="s">
+      <c r="I22" s="9" t="s">
         <v>72</v>
       </c>
       <c r="J22" s="1"/>
@@ -1277,11 +1302,12 @@
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
-      <c r="D23" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="E23" s="10"/>
-      <c r="F23" s="1"/>
+      <c r="E23" s="8">
+        <v>6</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>80</v>
+      </c>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
@@ -1292,13 +1318,12 @@
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
-      <c r="D24" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="F24" s="1"/>
+      <c r="E24" s="8">
+        <v>7</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>81</v>
+      </c>
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
@@ -1309,12 +1334,6 @@
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
-      <c r="D25" s="7">
-        <v>1</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>75</v>
-      </c>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
@@ -1326,12 +1345,6 @@
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
-      <c r="D26" s="7">
-        <v>2</v>
-      </c>
-      <c r="E26" s="8" t="s">
-        <v>76</v>
-      </c>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
@@ -1343,12 +1356,6 @@
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
-      <c r="D27" s="7">
-        <v>3</v>
-      </c>
-      <c r="E27" s="8" t="s">
-        <v>77</v>
-      </c>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
@@ -1360,12 +1367,6 @@
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
-      <c r="D28" s="7">
-        <v>4</v>
-      </c>
-      <c r="E28" s="8" t="s">
-        <v>78</v>
-      </c>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
@@ -1377,12 +1378,6 @@
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
-      <c r="D29" s="7">
-        <v>5</v>
-      </c>
-      <c r="E29" s="8" t="s">
-        <v>79</v>
-      </c>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
@@ -1394,12 +1389,6 @@
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
-      <c r="D30" s="7">
-        <v>6</v>
-      </c>
-      <c r="E30" s="8" t="s">
-        <v>80</v>
-      </c>
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
@@ -1411,12 +1400,6 @@
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
-      <c r="D31" s="7">
-        <v>7</v>
-      </c>
-      <c r="E31" s="8" t="s">
-        <v>81</v>
-      </c>
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
@@ -1425,10 +1408,9 @@
       <c r="K31" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="2">
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="H16:I16"/>
-    <mergeCell ref="D23:E23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
